--- a/Shablon/33622A.xlsx
+++ b/Shablon/33622A.xlsx
@@ -19,16 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="177">
-  <si>
-    <t>АО "Гос МКБ "Вымпел" им. И.И. Торопова"</t>
-  </si>
-  <si>
-    <t>125424, г.Москва, Волоколамское шоссе, дом 90, стр. 23</t>
-  </si>
-  <si>
-    <t>Тел.+7 (495) 491-05-31, 22-68, e-mail: ogmetr@vympelmkb.com</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="172">
   <si>
     <t>Условия проведения калибровки:</t>
   </si>
@@ -193,12 +184,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>СГМетр, лаборатория средств электрических и радиотехнических измерений</t>
-  </si>
-  <si>
-    <t>Уникальный номер об аккредитации в реестре акредитованных лиц № РОСС СОБ 3.00231.2014</t>
   </si>
   <si>
     <t>Заключение:</t>
@@ -1074,9 +1059,57 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1086,35 +1119,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1122,66 +1134,39 @@
     <xf numFmtId="168" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1499,77 +1484,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
+      <c r="A1" s="79"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="74" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
+      <c r="A5" s="88"/>
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="79" t="str">
+      <c r="A7" s="85" t="str">
         <f>"Протокол поверки № 10/"&amp;C102&amp;"/"&amp;D10</f>
         <v>Протокол поверки № 10/_date/_numb</v>
       </c>
-      <c r="B7" s="79"/>
-      <c r="C7" s="79"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="79"/>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="79"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="85"/>
+      <c r="G7" s="85"/>
+      <c r="H7" s="85"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
@@ -1582,29 +1557,29 @@
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="70"/>
-      <c r="C9" s="70"/>
+      <c r="A9" s="86" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="86"/>
+      <c r="C9" s="86"/>
       <c r="D9" s="31" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="33"/>
       <c r="G9" s="45" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H9" s="34"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="70"/>
-      <c r="C10" s="70"/>
+      <c r="A10" s="86" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
       <c r="D10" s="46" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
@@ -1612,11 +1587,11 @@
       <c r="H10" s="34"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="70" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
+      <c r="A11" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="86"/>
+      <c r="C11" s="86"/>
       <c r="D11" s="35">
         <v>2023</v>
       </c>
@@ -1626,13 +1601,13 @@
       <c r="H11" s="34"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="70" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="70"/>
-      <c r="C12" s="70"/>
+      <c r="A12" s="86" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
       <c r="D12" s="35" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E12" s="32"/>
       <c r="F12" s="32"/>
@@ -1640,13 +1615,13 @@
       <c r="H12" s="34"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="70" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="70"/>
-      <c r="C13" s="70"/>
+      <c r="A13" s="86" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
       <c r="D13" s="46" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E13" s="32"/>
       <c r="F13" s="32"/>
@@ -1654,13 +1629,13 @@
       <c r="H13" s="34"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="70" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
+      <c r="A14" s="86" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
       <c r="D14" s="36" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E14" s="32"/>
       <c r="F14" s="32"/>
@@ -1668,13 +1643,13 @@
       <c r="H14" s="34"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="70" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="70"/>
-      <c r="C15" s="70"/>
+      <c r="A15" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="86"/>
+      <c r="C15" s="86"/>
       <c r="D15" s="31" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E15" s="32"/>
       <c r="F15" s="32"/>
@@ -1692,103 +1667,103 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="69" t="s">
+      <c r="A18" s="87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="87"/>
+      <c r="C18" s="87"/>
+      <c r="D18" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="69"/>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69" t="s">
+      <c r="E18" s="87"/>
+      <c r="F18" s="87" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="87"/>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="83" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="84"/>
+      <c r="F19" s="87" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="87"/>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="83"/>
+      <c r="C20" s="83"/>
+      <c r="D20" s="84" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="84"/>
+      <c r="F20" s="87" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="87"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="84" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="84"/>
+      <c r="F21" s="87" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="87"/>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="69"/>
-      <c r="F18" s="69" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="69"/>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="73"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="72" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="72"/>
-      <c r="F19" s="69" t="s">
+      <c r="B22" s="83"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="84">
+        <v>220.1</v>
+      </c>
+      <c r="E22" s="84"/>
+      <c r="F22" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="69"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="73" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="72" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="72"/>
-      <c r="F20" s="69" t="s">
+      <c r="G22" s="87"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="83"/>
+      <c r="C23" s="83"/>
+      <c r="D23" s="84">
+        <v>50</v>
+      </c>
+      <c r="E23" s="84"/>
+      <c r="F23" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="G20" s="69"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="72"/>
-      <c r="F21" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="69"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="73" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="73"/>
-      <c r="C22" s="73"/>
-      <c r="D22" s="72">
-        <v>220.1</v>
-      </c>
-      <c r="E22" s="72"/>
-      <c r="F22" s="69" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="69"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="73" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="73"/>
-      <c r="C23" s="73"/>
-      <c r="D23" s="72">
-        <v>50</v>
-      </c>
-      <c r="E23" s="72"/>
-      <c r="F23" s="69" t="s">
-        <v>21</v>
-      </c>
-      <c r="G23" s="69"/>
+      <c r="G23" s="87"/>
       <c r="H23" s="7"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -1803,7 +1778,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B25" s="29"/>
       <c r="C25" s="29"/>
@@ -1825,17 +1800,17 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -1847,7 +1822,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -1859,154 +1834,154 @@
     </row>
     <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="52"/>
+      <c r="F31" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="B31" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="52" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="52"/>
-      <c r="F31" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="G31" s="58"/>
+      <c r="G31" s="54"/>
     </row>
     <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="52"/>
-      <c r="B32" s="53"/>
-      <c r="C32" s="55"/>
+      <c r="B32" s="66"/>
+      <c r="C32" s="71"/>
       <c r="D32" s="52"/>
       <c r="E32" s="52"/>
-      <c r="F32" s="59"/>
-      <c r="G32" s="60"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="52"/>
-      <c r="B33" s="53"/>
-      <c r="C33" s="56"/>
+      <c r="B33" s="66"/>
+      <c r="C33" s="72"/>
       <c r="D33" s="44" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="F33" s="61"/>
-      <c r="G33" s="62"/>
+        <v>124</v>
+      </c>
+      <c r="F33" s="57"/>
+      <c r="G33" s="58"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="54" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="80">
+      <c r="A34" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="73">
         <v>1</v>
       </c>
       <c r="C34" s="43">
         <v>10</v>
       </c>
       <c r="D34" s="47" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E34" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" s="64"/>
+        <v>117</v>
+      </c>
+      <c r="F34" s="59" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="60"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="55"/>
-      <c r="B35" s="81"/>
+      <c r="A35" s="71"/>
+      <c r="B35" s="74"/>
       <c r="C35" s="43">
         <v>10000000</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E35" s="51" t="s">
-        <v>123</v>
-      </c>
-      <c r="F35" s="63" t="s">
-        <v>56</v>
-      </c>
-      <c r="G35" s="64"/>
+        <v>118</v>
+      </c>
+      <c r="F35" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="G35" s="60"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="55"/>
-      <c r="B36" s="81"/>
+      <c r="A36" s="71"/>
+      <c r="B36" s="74"/>
       <c r="C36" s="43">
         <v>30000000</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E36" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="F36" s="65" t="s">
-        <v>57</v>
-      </c>
-      <c r="G36" s="66"/>
+        <v>119</v>
+      </c>
+      <c r="F36" s="61" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="62"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="55"/>
-      <c r="B37" s="81"/>
+      <c r="A37" s="71"/>
+      <c r="B37" s="74"/>
       <c r="C37" s="43">
         <v>60000000</v>
       </c>
       <c r="D37" s="51" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E37" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="F37" s="67" t="s">
-        <v>58</v>
-      </c>
-      <c r="G37" s="68"/>
+        <v>120</v>
+      </c>
+      <c r="F37" s="76" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" s="77"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="55"/>
-      <c r="B38" s="81"/>
+      <c r="A38" s="71"/>
+      <c r="B38" s="74"/>
       <c r="C38" s="43">
         <v>80000000</v>
       </c>
       <c r="D38" s="51" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E38" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="F38" s="63" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" s="64"/>
+        <v>121</v>
+      </c>
+      <c r="F38" s="59" t="s">
+        <v>54</v>
+      </c>
+      <c r="G38" s="60"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="56"/>
-      <c r="B39" s="82"/>
+      <c r="A39" s="72"/>
+      <c r="B39" s="75"/>
       <c r="C39" s="43">
         <v>120000000</v>
       </c>
       <c r="D39" s="50" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E39" s="50" t="s">
-        <v>127</v>
-      </c>
-      <c r="F39" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="G39" s="64"/>
+        <v>122</v>
+      </c>
+      <c r="F39" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="G39" s="60"/>
     </row>
     <row r="41" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -2018,51 +1993,51 @@
     </row>
     <row r="42" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="B42" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="C42" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" s="57" t="s">
-        <v>65</v>
-      </c>
-      <c r="E42" s="58"/>
-      <c r="F42" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="G42" s="58"/>
+        <v>58</v>
+      </c>
+      <c r="B42" s="66" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" s="67" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="E42" s="54"/>
+      <c r="F42" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="G42" s="54"/>
       <c r="H42" s="9"/>
     </row>
     <row r="43" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="52"/>
-      <c r="B43" s="53"/>
-      <c r="C43" s="84"/>
-      <c r="D43" s="61"/>
-      <c r="E43" s="62"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="60"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="68"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="56"/>
       <c r="H43" s="9"/>
     </row>
     <row r="44" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="52"/>
-      <c r="B44" s="53"/>
-      <c r="C44" s="85"/>
+      <c r="B44" s="66"/>
+      <c r="C44" s="69"/>
       <c r="D44" s="44" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E44" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="F44" s="61"/>
-      <c r="G44" s="62"/>
+        <v>124</v>
+      </c>
+      <c r="F44" s="57"/>
+      <c r="G44" s="58"/>
       <c r="H44" s="9"/>
     </row>
     <row r="45" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="52" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B45" s="38">
         <v>1.1279999999999999</v>
@@ -2071,15 +2046,15 @@
         <v>0.4</v>
       </c>
       <c r="D45" s="48" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>131</v>
-      </c>
-      <c r="F45" s="63" t="s">
-        <v>66</v>
-      </c>
-      <c r="G45" s="64"/>
+        <v>126</v>
+      </c>
+      <c r="F45" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="G45" s="60"/>
       <c r="H45" s="9"/>
     </row>
     <row r="46" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2091,15 +2066,15 @@
         <v>1</v>
       </c>
       <c r="D46" s="48" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F46" s="63" t="s">
-        <v>67</v>
-      </c>
-      <c r="G46" s="64"/>
+        <v>128</v>
+      </c>
+      <c r="F46" s="59" t="s">
+        <v>62</v>
+      </c>
+      <c r="G46" s="60"/>
       <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2111,15 +2086,15 @@
         <v>2.5</v>
       </c>
       <c r="D47" s="48" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="F47" s="65" t="s">
-        <v>68</v>
-      </c>
-      <c r="G47" s="66"/>
+        <v>130</v>
+      </c>
+      <c r="F47" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="G47" s="62"/>
       <c r="H47" s="9"/>
     </row>
     <row r="48" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2131,15 +2106,15 @@
         <v>7</v>
       </c>
       <c r="D48" s="48" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E48" s="48" t="s">
-        <v>137</v>
-      </c>
-      <c r="F48" s="67" t="s">
-        <v>69</v>
-      </c>
-      <c r="G48" s="68"/>
+        <v>132</v>
+      </c>
+      <c r="F48" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" s="77"/>
       <c r="H48" s="9"/>
     </row>
     <row r="49" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2194,7 +2169,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B54" s="14"/>
       <c r="C54" s="15"/>
@@ -2204,95 +2179,95 @@
     </row>
     <row r="55" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="52" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="C55" s="54"/>
+      <c r="D55" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" s="54"/>
+      <c r="F55" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="B55" s="57" t="s">
-        <v>72</v>
-      </c>
-      <c r="C55" s="58"/>
-      <c r="D55" s="57" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" s="58"/>
-      <c r="F55" s="57" t="s">
-        <v>54</v>
-      </c>
-      <c r="G55" s="58"/>
+      <c r="G55" s="54"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="52"/>
-      <c r="B56" s="59"/>
-      <c r="C56" s="60"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="62"/>
-      <c r="F56" s="59"/>
-      <c r="G56" s="60"/>
+      <c r="B56" s="55"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="56"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="52"/>
-      <c r="B57" s="61"/>
-      <c r="C57" s="62"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="58"/>
       <c r="D57" s="44" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E57" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="F57" s="61"/>
-      <c r="G57" s="62"/>
+        <v>124</v>
+      </c>
+      <c r="F57" s="57"/>
+      <c r="G57" s="58"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="52" t="s">
-        <v>71</v>
-      </c>
-      <c r="B58" s="87">
+        <v>66</v>
+      </c>
+      <c r="B58" s="63">
         <v>0</v>
       </c>
-      <c r="C58" s="88"/>
+      <c r="C58" s="64"/>
       <c r="D58" s="48" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E58" s="48" t="s">
-        <v>139</v>
-      </c>
-      <c r="F58" s="63" t="s">
-        <v>74</v>
-      </c>
-      <c r="G58" s="64"/>
+        <v>134</v>
+      </c>
+      <c r="F58" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="G58" s="60"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="52"/>
-      <c r="B59" s="87">
+      <c r="B59" s="63">
         <v>0.5</v>
       </c>
-      <c r="C59" s="88"/>
+      <c r="C59" s="64"/>
       <c r="D59" s="48" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="F59" s="63" t="s">
-        <v>75</v>
-      </c>
-      <c r="G59" s="64"/>
+        <v>136</v>
+      </c>
+      <c r="F59" s="59" t="s">
+        <v>70</v>
+      </c>
+      <c r="G59" s="60"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="52"/>
-      <c r="B60" s="87">
+      <c r="B60" s="63">
         <v>10</v>
       </c>
-      <c r="C60" s="88"/>
+      <c r="C60" s="64"/>
       <c r="D60" s="48" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E60" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="F60" s="65" t="s">
-        <v>76</v>
-      </c>
-      <c r="G60" s="66"/>
+        <v>138</v>
+      </c>
+      <c r="F60" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="G60" s="62"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="19"/>
@@ -2304,7 +2279,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="19" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B62" s="13"/>
       <c r="C62" s="15"/>
@@ -2314,21 +2289,21 @@
     </row>
     <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="52" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B63" s="52" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C63" s="52" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D63" s="52"/>
       <c r="E63" s="52" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F63" s="52"/>
       <c r="G63" s="52" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -2344,52 +2319,52 @@
       <c r="A65" s="52"/>
       <c r="B65" s="52"/>
       <c r="C65" s="40" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D65" s="40" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E65" s="40" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F65" s="40" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G65" s="52"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" s="86" t="s">
-        <v>79</v>
+      <c r="A66" s="65" t="s">
+        <v>74</v>
       </c>
       <c r="B66" s="38">
         <v>1E-3</v>
       </c>
       <c r="C66" s="48" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D66" s="48" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E66" s="39" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" s="86"/>
+      <c r="A67" s="65"/>
       <c r="B67" s="41">
         <v>1</v>
       </c>
       <c r="C67" s="48" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D67" s="48" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E67" s="39" t="e">
         <f>C67-$C$66</f>
@@ -2400,19 +2375,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="86"/>
+      <c r="A68" s="65"/>
       <c r="B68" s="41">
         <v>5</v>
       </c>
       <c r="C68" s="48" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D68" s="48" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E68" s="39" t="e">
         <f>C68-$C$66</f>
@@ -2423,19 +2398,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="86"/>
+      <c r="A69" s="65"/>
       <c r="B69" s="41">
         <v>10</v>
       </c>
       <c r="C69" s="48" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D69" s="48" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E69" s="39" t="e">
         <f t="shared" ref="E69:E80" si="1">C69-$C$66</f>
@@ -2446,19 +2421,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G69" s="37" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="86"/>
+      <c r="A70" s="65"/>
       <c r="B70" s="41">
         <v>20</v>
       </c>
       <c r="C70" s="48" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D70" s="48" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E70" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2469,19 +2444,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G70" s="37" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="86"/>
+      <c r="A71" s="65"/>
       <c r="B71" s="41">
         <v>30</v>
       </c>
       <c r="C71" s="48" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D71" s="48" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E71" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2492,19 +2467,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G71" s="37" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="86"/>
+      <c r="A72" s="65"/>
       <c r="B72" s="41">
         <v>40</v>
       </c>
       <c r="C72" s="48" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D72" s="48" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E72" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2515,19 +2490,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G72" s="37" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="86"/>
+      <c r="A73" s="65"/>
       <c r="B73" s="41">
         <v>50</v>
       </c>
       <c r="C73" s="48" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D73" s="48" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E73" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2538,19 +2513,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G73" s="37" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="86"/>
+      <c r="A74" s="65"/>
       <c r="B74" s="41">
         <v>60</v>
       </c>
       <c r="C74" s="48" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D74" s="48" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E74" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2561,19 +2536,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G74" s="37" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="86"/>
+      <c r="A75" s="65"/>
       <c r="B75" s="41">
         <v>70</v>
       </c>
       <c r="C75" s="48" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D75" s="48" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E75" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2584,19 +2559,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="86"/>
+      <c r="A76" s="65"/>
       <c r="B76" s="41">
         <v>80</v>
       </c>
       <c r="C76" s="48" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D76" s="48" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E76" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2607,19 +2582,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G76" s="37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="86"/>
+      <c r="A77" s="65"/>
       <c r="B77" s="41">
         <v>90</v>
       </c>
       <c r="C77" s="48" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D77" s="48" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E77" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2630,19 +2605,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G77" s="37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="86"/>
+      <c r="A78" s="65"/>
       <c r="B78" s="41">
         <v>100</v>
       </c>
       <c r="C78" s="48" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D78" s="48" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E78" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2653,19 +2628,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G78" s="37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="86"/>
+      <c r="A79" s="65"/>
       <c r="B79" s="41">
         <v>110</v>
       </c>
       <c r="C79" s="48" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D79" s="48" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E79" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2676,19 +2651,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G79" s="37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="86"/>
+      <c r="A80" s="65"/>
       <c r="B80" s="41">
         <v>120</v>
       </c>
       <c r="C80" s="48" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D80" s="48" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E80" s="39" t="e">
         <f t="shared" si="1"/>
@@ -2699,42 +2674,42 @@
         <v>#VALUE!</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="86" t="s">
-        <v>87</v>
+      <c r="A81" s="65" t="s">
+        <v>82</v>
       </c>
       <c r="B81" s="38">
         <v>1E-3</v>
       </c>
       <c r="C81" s="48" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D81" s="48" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E81" s="39" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F81" s="37" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A82" s="86"/>
+      <c r="A82" s="65"/>
       <c r="B82" s="41">
         <v>1</v>
       </c>
       <c r="C82" s="48" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D82" s="48" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E82" s="39" t="e">
         <f>C82-$C$81</f>
@@ -2745,19 +2720,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A83" s="86"/>
+      <c r="A83" s="65"/>
       <c r="B83" s="41">
         <v>5</v>
       </c>
       <c r="C83" s="48" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D83" s="48" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E83" s="39" t="e">
         <f t="shared" ref="E83:E95" si="2">C83-$C$81</f>
@@ -2768,19 +2743,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A84" s="86"/>
+      <c r="A84" s="65"/>
       <c r="B84" s="41">
         <v>10</v>
       </c>
       <c r="C84" s="48" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D84" s="48" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E84" s="39" t="e">
         <f t="shared" si="2"/>
@@ -2791,19 +2766,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A85" s="86"/>
+      <c r="A85" s="65"/>
       <c r="B85" s="41">
         <v>20</v>
       </c>
       <c r="C85" s="48" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D85" s="48" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E85" s="39" t="e">
         <f t="shared" si="2"/>
@@ -2814,19 +2789,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A86" s="86"/>
+      <c r="A86" s="65"/>
       <c r="B86" s="41">
         <v>30</v>
       </c>
       <c r="C86" s="48" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D86" s="48" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E86" s="39" t="e">
         <f t="shared" si="2"/>
@@ -2837,19 +2812,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A87" s="86"/>
+      <c r="A87" s="65"/>
       <c r="B87" s="41">
         <v>40</v>
       </c>
       <c r="C87" s="48" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D87" s="48" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E87" s="39" t="e">
         <f t="shared" si="2"/>
@@ -2860,19 +2835,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A88" s="86"/>
+      <c r="A88" s="65"/>
       <c r="B88" s="41">
         <v>50</v>
       </c>
       <c r="C88" s="48" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D88" s="48" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E88" s="39" t="e">
         <f t="shared" si="2"/>
@@ -2883,19 +2858,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" s="86"/>
+      <c r="A89" s="65"/>
       <c r="B89" s="41">
         <v>60</v>
       </c>
       <c r="C89" s="48" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D89" s="48" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="E89" s="39" t="e">
         <f t="shared" si="2"/>
@@ -2906,19 +2881,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="86"/>
+      <c r="A90" s="65"/>
       <c r="B90" s="41">
         <v>70</v>
       </c>
       <c r="C90" s="48" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D90" s="48" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E90" s="39" t="e">
         <f t="shared" si="2"/>
@@ -2929,19 +2904,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="86"/>
+      <c r="A91" s="65"/>
       <c r="B91" s="41">
         <v>80</v>
       </c>
       <c r="C91" s="48" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D91" s="48" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E91" s="39" t="e">
         <f t="shared" si="2"/>
@@ -2952,19 +2927,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="86"/>
+      <c r="A92" s="65"/>
       <c r="B92" s="41">
         <v>90</v>
       </c>
       <c r="C92" s="48" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D92" s="48" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E92" s="39" t="e">
         <f t="shared" si="2"/>
@@ -2975,19 +2950,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="86"/>
+      <c r="A93" s="65"/>
       <c r="B93" s="41">
         <v>100</v>
       </c>
       <c r="C93" s="48" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D93" s="48" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E93" s="39" t="e">
         <f t="shared" si="2"/>
@@ -2998,19 +2973,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="86"/>
+      <c r="A94" s="65"/>
       <c r="B94" s="41">
         <v>110</v>
       </c>
       <c r="C94" s="48" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D94" s="48" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E94" s="39" t="e">
         <f t="shared" si="2"/>
@@ -3021,19 +2996,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="86"/>
+      <c r="A95" s="65"/>
       <c r="B95" s="41">
         <v>120</v>
       </c>
       <c r="C95" s="48" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D95" s="48" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E95" s="39" t="e">
         <f t="shared" si="2"/>
@@ -3044,7 +3019,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -3084,75 +3059,80 @@
       <c r="F99" s="18"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="75" t="s">
-        <v>44</v>
-      </c>
-      <c r="B100" s="75"/>
+      <c r="A100" s="78" t="s">
+        <v>39</v>
+      </c>
+      <c r="B100" s="78"/>
       <c r="C100" s="49" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
       <c r="F100" s="18"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="75" t="s">
-        <v>31</v>
-      </c>
-      <c r="B101" s="75"/>
+      <c r="A101" s="78" t="s">
+        <v>28</v>
+      </c>
+      <c r="B101" s="78"/>
       <c r="C101" s="26"/>
       <c r="D101" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E101" s="77" t="s">
-        <v>29</v>
-      </c>
-      <c r="F101" s="78"/>
+        <v>3</v>
+      </c>
+      <c r="E101" s="81" t="s">
+        <v>26</v>
+      </c>
+      <c r="F101" s="82"/>
       <c r="G101" s="11" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H101" s="28"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="75" t="s">
-        <v>5</v>
-      </c>
-      <c r="B102" s="75"/>
-      <c r="C102" s="76" t="s">
-        <v>30</v>
-      </c>
-      <c r="D102" s="76"/>
+      <c r="A102" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="B102" s="78"/>
+      <c r="C102" s="80" t="s">
+        <v>27</v>
+      </c>
+      <c r="D102" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="77">
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="F55:G57"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B55:C57"/>
-    <mergeCell ref="A81:A95"/>
-    <mergeCell ref="B63:B65"/>
-    <mergeCell ref="C63:D64"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A66:A80"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="D42:E43"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="B34:B39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="G63:G65"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="F31:G33"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F42:G44"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="D55:E56"/>
+    <mergeCell ref="E63:F64"/>
+    <mergeCell ref="D31:E32"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A4:H4"/>
     <mergeCell ref="A100:B100"/>
     <mergeCell ref="A102:B102"/>
     <mergeCell ref="A3:H3"/>
@@ -3169,39 +3149,34 @@
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D22:E22"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="G63:G65"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="F31:G33"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F42:G44"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="D55:E56"/>
-    <mergeCell ref="E63:F64"/>
-    <mergeCell ref="D31:E32"/>
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="B34:B39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="D42:E43"/>
+    <mergeCell ref="A81:A95"/>
+    <mergeCell ref="B63:B65"/>
+    <mergeCell ref="C63:D64"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A66:A80"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="F55:G57"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B55:C57"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.39370078740157483" bottom="0.61458333333333337" header="0.39370078740157483" footer="0.39370078740157483"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180" r:id="rId1"/>
